--- a/data/trans_camb/Hacinamiento_R-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/Hacinamiento_R-Habitat-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,51; 10,3</t>
+          <t>-1,96; 10,24</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,49; 13,36</t>
+          <t>-0,01; 13,23</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-5,17; 4,71</t>
+          <t>-4,54; 5,37</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-4,25; 6,94</t>
+          <t>-3,32; 7,54</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-2,56; 8,81</t>
+          <t>-3,28; 9,06</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-6,59; 2,81</t>
+          <t>-6,32; 2,7</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-1,14; 6,69</t>
+          <t>-1,15; 6,8</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-0,24; 8,59</t>
+          <t>-0,02; 8,52</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-4,4; 2,2</t>
+          <t>-4,39; 2,52</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-31,26; 427,6</t>
+          <t>-37,71; 372,97</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-13,63; 552,41</t>
+          <t>-7,82; 546,46</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-75,3; 252,33</t>
+          <t>-69,25; 265,44</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-49,58; 160,18</t>
+          <t>-41,56; 198,45</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-36,76; 211,17</t>
+          <t>-41,41; 235,41</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-71,2; 78,95</t>
+          <t>-73,43; 64,3</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-17,46; 179,19</t>
+          <t>-19,28; 172,13</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-5,18; 223,12</t>
+          <t>-3,23; 223,66</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-60,53; 61,07</t>
+          <t>-57,14; 69,61</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,55; 10,74</t>
+          <t>-1,11; 10,57</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-3,45; 5,98</t>
+          <t>-3,82; 5,69</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-5,59; 3,2</t>
+          <t>-5,69; 3,38</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-5,53; 4,72</t>
+          <t>-5,26; 5,67</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-7,52; 1,76</t>
+          <t>-8,04; 1,49</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-5,58; 4,61</t>
+          <t>-5,45; 4,65</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-1,73; 5,62</t>
+          <t>-1,88; 5,87</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-4,42; 2,31</t>
+          <t>-4,13; 2,46</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-3,99; 2,48</t>
+          <t>-3,99; 2,74</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-10,32; 216,12</t>
+          <t>-12,99; 257,13</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-42,69; 145,8</t>
+          <t>-41,32; 150,39</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-59,87; 78,59</t>
+          <t>-59,93; 84,66</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-51,57; 84,45</t>
+          <t>-48,21; 107,64</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-67,8; 38,35</t>
+          <t>-70,55; 30,89</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-51,17; 85,88</t>
+          <t>-50,79; 92,33</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-18,26; 96,35</t>
+          <t>-20,4; 108,69</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-47,08; 43,82</t>
+          <t>-45,15; 42,99</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-42,71; 44,37</t>
+          <t>-42,8; 47,74</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,25; 14,7</t>
+          <t>0,58; 14,17</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,12; 9,37</t>
+          <t>-2,71; 9,24</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-7,09; 2,66</t>
+          <t>-6,8; 3,03</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,47; 14,35</t>
+          <t>0,76; 13,95</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-4,03; 6,83</t>
+          <t>-3,64; 6,47</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-1,34; 9,49</t>
+          <t>-1,09; 9,89</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,75; 12,05</t>
+          <t>2,83; 12,04</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-2,03; 5,76</t>
+          <t>-1,58; 5,91</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-2,68; 4,88</t>
+          <t>-3,27; 4,76</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>6,61; 329,19</t>
+          <t>4,35; 313,49</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-24,62; 203,92</t>
+          <t>-28,38; 200,25</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-68,26; 68,85</t>
+          <t>-68,48; 74,77</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>9,61; 433,46</t>
+          <t>-1,94; 372,24</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-49,19; 197,56</t>
+          <t>-47,24; 198,26</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-21,04; 304,73</t>
+          <t>-16,62; 270,57</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>27,14; 252,93</t>
+          <t>31,44; 265,34</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-23,63; 123,17</t>
+          <t>-21,58; 125,7</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-30,36; 109,9</t>
+          <t>-34,88; 103,35</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-4,95; 4,71</t>
+          <t>-5,77; 4,22</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-5,65; 4,15</t>
+          <t>-5,62; 4,27</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-4,23; 5,37</t>
+          <t>-5,29; 5,05</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-8,2; 3,19</t>
+          <t>-7,5; 3,31</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-9,81; 0,32</t>
+          <t>-9,5; 0,51</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-6,97; 4,02</t>
+          <t>-6,42; 4,91</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-4,97; 2,12</t>
+          <t>-4,57; 2,23</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-6,26; 1,04</t>
+          <t>-5,79; 1,12</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-4,08; 3,36</t>
+          <t>-3,93; 3,32</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-52,94; 106,4</t>
+          <t>-58,74; 84,02</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-55,44; 94,94</t>
+          <t>-57,11; 87,67</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-43,37; 121,31</t>
+          <t>-50,17; 100,96</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-60,37; 42,87</t>
+          <t>-57,54; 46,62</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-73,66; 4,03</t>
+          <t>-71,12; 8,67</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-51,53; 52,59</t>
+          <t>-49,08; 61,75</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-45,65; 31,97</t>
+          <t>-44,5; 31,21</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-56,8; 15,95</t>
+          <t>-54,39; 15,99</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-37,53; 48,31</t>
+          <t>-36,96; 48,92</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,45; 6,41</t>
+          <t>0,75; 6,63</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-0,95; 4,66</t>
+          <t>-1,0; 4,65</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-2,96; 1,77</t>
+          <t>-3,05; 2,02</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-1,78; 4,07</t>
+          <t>-1,63; 4,02</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-3,93; 1,15</t>
+          <t>-4,03; 1,12</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-2,45; 3,01</t>
+          <t>-2,51; 2,77</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0,3; 4,26</t>
+          <t>0,36; 4,44</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-1,49; 2,02</t>
+          <t>-1,62; 2,07</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-1,83; 1,73</t>
+          <t>-1,89; 1,61</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>3,02; 118,21</t>
+          <t>8,41; 121,93</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-12,62; 85,52</t>
+          <t>-13,27; 86,89</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-37,86; 33,79</t>
+          <t>-38,75; 40,44</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-20,85; 58,71</t>
+          <t>-17,65; 61,61</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-41,85; 18,43</t>
+          <t>-43,07; 18,13</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-26,96; 44,99</t>
+          <t>-26,87; 42,87</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>4,12; 67,99</t>
+          <t>4,03; 71,64</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-18,8; 33,18</t>
+          <t>-20,48; 31,94</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-22,31; 26,33</t>
+          <t>-22,89; 25,69</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/Hacinamiento_R-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/Hacinamiento_R-Habitat-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,96; 10,24</t>
+          <t>-1,92; 10,79</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,01; 13,23</t>
+          <t>0,11; 12,32</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-4,54; 5,37</t>
+          <t>-4,85; 4,97</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-3,32; 7,54</t>
+          <t>-3,77; 6,93</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-3,28; 9,06</t>
+          <t>-3,3; 8,1</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-6,32; 2,7</t>
+          <t>-6,83; 2,81</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-1,15; 6,8</t>
+          <t>-1,38; 6,36</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-0,02; 8,52</t>
+          <t>-0,52; 8,49</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-4,39; 2,52</t>
+          <t>-4,17; 2,47</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-37,71; 372,97</t>
+          <t>-28,08; 451,03</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-7,82; 546,46</t>
+          <t>-13,86; 480,35</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-69,25; 265,44</t>
+          <t>-70,51; 224,04</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-41,56; 198,45</t>
+          <t>-45,36; 173,17</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-41,41; 235,41</t>
+          <t>-43,18; 202,75</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-73,43; 64,3</t>
+          <t>-74,27; 74,69</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-19,28; 172,13</t>
+          <t>-21,72; 160,56</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-3,23; 223,66</t>
+          <t>-8,33; 210,38</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-57,14; 69,61</t>
+          <t>-58,35; 61,17</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,11; 10,57</t>
+          <t>-1,32; 10,19</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-3,82; 5,69</t>
+          <t>-3,72; 5,82</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-5,69; 3,38</t>
+          <t>-5,46; 3,54</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-5,26; 5,67</t>
+          <t>-5,12; 4,7</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-8,04; 1,49</t>
+          <t>-7,66; 1,9</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-5,45; 4,65</t>
+          <t>-5,2; 5,07</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-1,88; 5,87</t>
+          <t>-2,04; 5,88</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-4,13; 2,46</t>
+          <t>-4,08; 2,46</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-3,99; 2,74</t>
+          <t>-3,69; 3,27</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-12,99; 257,13</t>
+          <t>-21,22; 232,73</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-41,32; 150,39</t>
+          <t>-42,84; 133,31</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-59,93; 84,66</t>
+          <t>-59,01; 94,83</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-48,21; 107,64</t>
+          <t>-47,86; 94,1</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-70,55; 30,89</t>
+          <t>-67,67; 43,82</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-50,79; 92,33</t>
+          <t>-49,0; 94,74</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-20,4; 108,69</t>
+          <t>-23,37; 95,54</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-45,15; 42,99</t>
+          <t>-46,99; 42,2</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-42,8; 47,74</t>
+          <t>-41,24; 60,43</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,58; 14,17</t>
+          <t>1,27; 14,91</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,71; 9,24</t>
+          <t>-2,6; 8,86</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-6,8; 3,03</t>
+          <t>-7,11; 3,05</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,76; 13,95</t>
+          <t>1,36; 13,88</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-3,64; 6,47</t>
+          <t>-4,18; 6,39</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-1,09; 9,89</t>
+          <t>-1,01; 10,53</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,83; 12,04</t>
+          <t>3,0; 12,39</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-1,58; 5,91</t>
+          <t>-1,77; 6,22</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-3,27; 4,76</t>
+          <t>-2,5; 4,74</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>4,35; 313,49</t>
+          <t>5,74; 316,36</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-28,38; 200,25</t>
+          <t>-28,45; 199,85</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-68,48; 74,77</t>
+          <t>-70,62; 77,49</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-1,94; 372,24</t>
+          <t>10,03; 343,96</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-47,24; 198,26</t>
+          <t>-56,05; 178,25</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-16,62; 270,57</t>
+          <t>-17,12; 296,58</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>31,44; 265,34</t>
+          <t>32,36; 257,73</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-21,58; 125,7</t>
+          <t>-23,2; 131,56</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-34,88; 103,35</t>
+          <t>-31,78; 100,1</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-5,77; 4,22</t>
+          <t>-5,52; 4,44</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-5,62; 4,27</t>
+          <t>-5,52; 4,38</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-5,29; 5,05</t>
+          <t>-4,71; 5,14</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-7,5; 3,31</t>
+          <t>-7,91; 3,23</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-9,5; 0,51</t>
+          <t>-10,13; 0,64</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-6,42; 4,91</t>
+          <t>-6,68; 4,71</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-4,57; 2,23</t>
+          <t>-4,84; 2,42</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-5,79; 1,12</t>
+          <t>-5,91; 0,96</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-3,93; 3,32</t>
+          <t>-3,98; 3,26</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-58,74; 84,02</t>
+          <t>-58,31; 92,01</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-57,11; 87,67</t>
+          <t>-58,31; 99,63</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-50,17; 100,96</t>
+          <t>-48,02; 104,72</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-57,54; 46,62</t>
+          <t>-59,2; 44,44</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-71,12; 8,67</t>
+          <t>-71,33; 15,12</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-49,08; 61,75</t>
+          <t>-50,53; 64,76</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-44,5; 31,21</t>
+          <t>-45,05; 39,09</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-54,39; 15,99</t>
+          <t>-56,29; 14,02</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-36,96; 48,92</t>
+          <t>-36,84; 44,89</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,75; 6,63</t>
+          <t>0,79; 6,62</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-1,0; 4,65</t>
+          <t>-0,64; 4,84</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-3,05; 2,02</t>
+          <t>-3,15; 1,68</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-1,63; 4,02</t>
+          <t>-1,56; 3,88</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-4,03; 1,12</t>
+          <t>-4,03; 1,21</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-2,51; 2,77</t>
+          <t>-2,49; 3,16</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0,36; 4,44</t>
+          <t>0,35; 4,35</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-1,62; 2,07</t>
+          <t>-1,8; 1,88</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-1,89; 1,61</t>
+          <t>-1,84; 1,72</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>8,41; 121,93</t>
+          <t>9,1; 128,79</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-13,27; 86,89</t>
+          <t>-10,37; 95,68</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-38,75; 40,44</t>
+          <t>-39,24; 30,35</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-17,65; 61,61</t>
+          <t>-17,05; 56,53</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-43,07; 18,13</t>
+          <t>-42,73; 18,61</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-26,87; 42,87</t>
+          <t>-27,34; 46,24</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>4,03; 71,64</t>
+          <t>3,38; 67,98</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-20,48; 31,94</t>
+          <t>-22,45; 28,57</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-22,89; 25,69</t>
+          <t>-22,85; 27,28</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/Hacinamiento_R-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/Hacinamiento_R-Habitat-trans_camb.xlsx
@@ -529,14 +529,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -624,32 +624,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>1,32</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>2,19</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>-1,96</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>4,04</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>5,9</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>-0,07</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>1,32</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>2,19</t>
-        </is>
-      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-1,92</t>
+          <t>0,12</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-1,05</t>
+          <t>-0,97</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-1,92; 10,79</t>
+          <t>-4,25; 6,94</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,11; 12,32</t>
+          <t>-2,56; 8,81</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-4,85; 4,97</t>
+          <t>-6,65; 2,72</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-3,77; 6,93</t>
+          <t>-1,51; 10,3</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-3,3; 8,1</t>
+          <t>-0,49; 13,36</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-6,83; 2,81</t>
+          <t>-4,96; 5,08</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-1,38; 6,36</t>
+          <t>-1,14; 6,69</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-0,52; 8,49</t>
+          <t>-0,24; 8,59</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-4,17; 2,47</t>
+          <t>-4,25; 2,23</t>
         </is>
       </c>
     </row>
@@ -730,32 +730,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>20,54%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>34,13%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>-30,57%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>86,68%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>126,65%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>-1,48%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>20,54%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>34,13%</t>
-        </is>
-      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-30,02%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-18,85%</t>
+          <t>-17,45%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-28,08; 451,03</t>
+          <t>-49,58; 160,18</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-13,86; 480,35</t>
+          <t>-36,76; 211,17</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-70,51; 224,04</t>
+          <t>-72,8; 80,42</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-45,36; 173,17</t>
+          <t>-31,26; 427,6</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-43,18; 202,75</t>
+          <t>-13,63; 552,41</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-74,27; 74,69</t>
+          <t>-74,43; 263,42</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-21,72; 160,56</t>
+          <t>-17,46; 179,19</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-8,33; 210,38</t>
+          <t>-5,18; 223,12</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-58,35; 61,17</t>
+          <t>-61,7; 60,3</t>
         </is>
       </c>
     </row>
@@ -840,32 +840,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>-0,16</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>-2,58</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>-0,64</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>4,65</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>0,95</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-0,98</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>-0,16</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>-2,58</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-0,29</t>
+          <t>-1,47</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-0,52</t>
+          <t>-0,95</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,32; 10,19</t>
+          <t>-5,53; 4,72</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-3,72; 5,82</t>
+          <t>-7,52; 1,76</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-5,46; 3,54</t>
+          <t>-5,64; 4,24</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-5,12; 4,7</t>
+          <t>-0,55; 10,74</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-7,66; 1,9</t>
+          <t>-3,45; 5,98</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-5,2; 5,07</t>
+          <t>-6,41; 2,43</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-2,04; 5,88</t>
+          <t>-1,73; 5,62</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-4,08; 2,46</t>
+          <t>-4,42; 2,31</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-3,69; 3,27</t>
+          <t>-4,4; 2,03</t>
         </is>
       </c>
     </row>
@@ -946,32 +946,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>-2,02%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>-31,89%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>-7,87%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>69,1%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>14,12%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-14,53%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-2,02%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>-31,89%</t>
-        </is>
-      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-3,61%</t>
+          <t>-21,82%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-7,02%</t>
+          <t>-12,75%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-21,22; 232,73</t>
+          <t>-51,57; 84,45</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-42,84; 133,31</t>
+          <t>-67,8; 38,35</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-59,01; 94,83</t>
+          <t>-53,5; 77,28</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-47,86; 94,1</t>
+          <t>-10,32; 216,12</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-67,67; 43,82</t>
+          <t>-42,69; 145,8</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-49,0; 94,74</t>
+          <t>-63,14; 62,75</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-23,37; 95,54</t>
+          <t>-18,26; 96,35</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-46,99; 42,2</t>
+          <t>-47,08; 43,82</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-41,24; 60,43</t>
+          <t>-46,13; 36,36</t>
         </is>
       </c>
     </row>
@@ -1056,32 +1056,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>7,36</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>1,31</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>3,63</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>7,64</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>3,49</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>-1,68</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>7,36</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>1,31</t>
-        </is>
-      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>4,37</t>
+          <t>-0,63</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>1,32</t>
+          <t>1,56</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,27; 14,91</t>
+          <t>1,47; 14,35</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,6; 8,86</t>
+          <t>-4,03; 6,83</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-7,11; 3,05</t>
+          <t>-2,09; 8,48</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,36; 13,88</t>
+          <t>1,25; 14,7</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-4,18; 6,39</t>
+          <t>-2,12; 9,37</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-1,01; 10,53</t>
+          <t>-5,82; 4,22</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,0; 12,39</t>
+          <t>2,75; 12,05</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-1,77; 6,22</t>
+          <t>-2,03; 5,76</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-2,5; 4,74</t>
+          <t>-2,41; 5,02</t>
         </is>
       </c>
     </row>
@@ -1162,32 +1162,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>125,02%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>22,22%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>61,57%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>108,14%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>49,39%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>-23,78%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>125,02%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>22,22%</t>
-        </is>
-      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>74,12%</t>
+          <t>-8,85%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>20,39%</t>
+          <t>24,19%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>5,74; 316,36</t>
+          <t>9,61; 433,46</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-28,45; 199,85</t>
+          <t>-49,19; 197,56</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-70,62; 77,49</t>
+          <t>-25,99; 286,5</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>10,03; 343,96</t>
+          <t>6,61; 329,19</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-56,05; 178,25</t>
+          <t>-24,62; 203,92</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-17,12; 296,58</t>
+          <t>-57,63; 110,73</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>32,36; 257,73</t>
+          <t>27,14; 252,93</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-23,2; 131,56</t>
+          <t>-23,63; 123,17</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-31,78; 100,1</t>
+          <t>-30,31; 105,68</t>
         </is>
       </c>
     </row>
@@ -1272,32 +1272,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>-2,18</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>-4,5</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>-1,24</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>-0,51</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>-0,56</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>0,52</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>-2,18</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>-4,5</t>
-        </is>
-      </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-1,13</t>
+          <t>1,29</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-0,23</t>
+          <t>0,07</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-5,52; 4,44</t>
+          <t>-8,2; 3,19</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-5,52; 4,38</t>
+          <t>-9,81; 0,32</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-4,71; 5,14</t>
+          <t>-7,12; 3,94</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-7,91; 3,23</t>
+          <t>-4,95; 4,71</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-10,13; 0,64</t>
+          <t>-5,65; 4,15</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-6,68; 4,71</t>
+          <t>-3,63; 5,97</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-4,84; 2,42</t>
+          <t>-4,97; 2,12</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-5,91; 0,96</t>
+          <t>-6,26; 1,04</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-3,98; 3,26</t>
+          <t>-3,85; 3,71</t>
         </is>
       </c>
     </row>
@@ -1378,32 +1378,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>-20,64%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>-42,66%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>-11,75%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>-7,0%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>-7,61%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>7,08%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>-20,64%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>-42,66%</t>
-        </is>
-      </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-10,72%</t>
+          <t>17,63%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-2,61%</t>
+          <t>0,79%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-58,31; 92,01</t>
+          <t>-60,37; 42,87</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-58,31; 99,63</t>
+          <t>-73,66; 4,03</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-48,02; 104,72</t>
+          <t>-51,96; 49,09</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-59,2; 44,44</t>
+          <t>-52,94; 106,4</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-71,33; 15,12</t>
+          <t>-55,44; 94,94</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-50,53; 64,76</t>
+          <t>-37,48; 139,97</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-45,05; 39,09</t>
+          <t>-45,65; 31,97</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-56,29; 14,02</t>
+          <t>-56,8; 15,95</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-36,84; 44,89</t>
+          <t>-35,42; 53,69</t>
         </is>
       </c>
     </row>
@@ -1488,32 +1488,32 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>1,19</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>-1,36</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>-0,12</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
           <t>3,6</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>1,96</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>-0,59</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>1,19</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>-1,36</t>
-        </is>
-      </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,19</t>
+          <t>-0,2</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,79; 6,62</t>
+          <t>-1,78; 4,07</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-0,64; 4,84</t>
+          <t>-3,93; 1,15</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-3,15; 1,68</t>
+          <t>-2,67; 2,66</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-1,56; 3,88</t>
+          <t>0,45; 6,41</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-4,03; 1,21</t>
+          <t>-0,95; 4,66</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-2,49; 3,16</t>
+          <t>-2,6; 2,2</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0,35; 4,35</t>
+          <t>0,3; 4,26</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-1,8; 1,88</t>
+          <t>-1,49; 2,02</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-1,84; 1,72</t>
+          <t>-1,8; 1,76</t>
         </is>
       </c>
     </row>
@@ -1594,32 +1594,32 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>14,94%</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>-17,02%</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>-1,51%</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
           <t>54,91%</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>29,88%</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>-8,99%</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>14,94%</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>-17,02%</t>
-        </is>
-      </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>-3,06%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>-1,92%</t>
+          <t>-1,87%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>9,1; 128,79</t>
+          <t>-20,85; 58,71</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-10,37; 95,68</t>
+          <t>-41,85; 18,43</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-39,24; 30,35</t>
+          <t>-29,43; 40,24</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-17,05; 56,53</t>
+          <t>3,02; 118,21</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-42,73; 18,61</t>
+          <t>-12,62; 85,52</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-27,34; 46,24</t>
+          <t>-34,19; 42,61</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>3,38; 67,98</t>
+          <t>4,12; 67,99</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-22,45; 28,57</t>
+          <t>-18,8; 33,18</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-22,85; 27,28</t>
+          <t>-22,53; 28,33</t>
         </is>
       </c>
     </row>
